--- a/data/raw/sales/Week 14/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 14/Nexlev/other_channels.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>ET-01 Black</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="D3" s="13" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>ET-02 Green</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D4" s="13" t="n">
@@ -762,7 +762,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="32" t="inlineStr">
         <is>
-          <t>FBA79347</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>GS-5</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -2590,7 +2590,7 @@
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -2730,7 +2730,7 @@
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>FBA79451</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>SS-01</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="D14" s="17" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="D31" s="17" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>NP-07-WD</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="D32" s="17" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D36" s="17" t="n">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>V-01-RG</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="D40" s="17" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D54" s="21" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E54" s="22" t="n">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D3" s="24" t="n">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>ET-02 GN</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D5" s="24" t="n">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D15" s="24" t="n">
@@ -7882,7 +7882,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
